--- a/artfynd/A 2126-2024 artfynd.xlsx
+++ b/artfynd/A 2126-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2126-2024 artfynd.xlsx
+++ b/artfynd/A 2126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114388769</v>
+        <v>114407866</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579762</v>
+        <v>579729</v>
       </c>
       <c r="R2" t="n">
-        <v>6406946</v>
+        <v>6406976</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,51 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114388683</v>
+        <v>114388769</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +834,10 @@
         <v>579762</v>
       </c>
       <c r="R3" t="n">
-        <v>6406983</v>
+        <v>6406946</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114407906</v>
+        <v>114407900</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,7 +921,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1014,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114517271</v>
+        <v>114388683</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,7 +1032,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579754</v>
+        <v>579762</v>
       </c>
       <c r="R5" t="n">
-        <v>6406987</v>
+        <v>6406983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1105,353 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114517271</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 2126, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579754</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406987</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114388612</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 2126, Svartsmörja, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579838</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6406958</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108226028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartsmörja O, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579829</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6406776</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vägkanten</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
